--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -1,71 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfeinstein\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DD0AAD3-E6C2-4C2E-9CF1-37E1BFDD4385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{CF7D4A7D-AFDD-47A7-8305-EA9FCA254F9C}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$F$70</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Hub</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -73,26 +53,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -412,16 +474,1574 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08032914-A696-480A-A89E-601ACF0B10D8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hub</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ANR-SE</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2.8799</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ANR-SW</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2.6174</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2.758</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2.758</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2.758</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Algonquin</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2.803</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2.803</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2.803</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CG-Mainline</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2.814</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2.826</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2.826</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2.826</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CG-Onshore</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2.8136</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2.795</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CIG</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1.815</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Cheyenne Hub</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1.815</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2.7246</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Consumers</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2.8088</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>EP West Texas</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1.7466</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Gas-South</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2.4222</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2.485</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Enable Gas</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2.8214</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2.832</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Enbridge-Dawn</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2.805</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FGT-Z3</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>4.5909</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>4.545</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>4.545</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>4.545</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2.7991</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>3.2871</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>3.285</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Iroquois (into)</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Iroquois-Z2</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2.8072</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Katy</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2.788</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Kern Delivered</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2.156</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Michcon</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2.8098</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.866</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2.866</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.866</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Millennium East Pool</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2.525</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>NGPL-Midcont Pool</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2.665</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2.6798</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.781</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>2.781</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2.781</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>NGPL-STX</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2.7689</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>NGPL-TxOk</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2.7496</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>NNG-Demarc</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>NNG-Ventura</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2.6808</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>NWP-Rockies</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NWP-Sumas</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1.572</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ONEOK</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2.6526</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>PG&amp;E-Citygate</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1.9591</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PGT-Malin</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1.3192</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Panhandle</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2.6338</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Permian (EP)</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1.7958</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Pine Prairie</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2.9677</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2.992</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>REX-Z3</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2.7289</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2.785</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>San Juan (EP)</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2.007</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>2.135</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Socal-Border</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2.5482</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>2.485</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Socal-Citygate</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>3.2201</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>3.375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Sonat-Z0</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>4.315</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4.4174</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>4.363</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Southern Star</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2.6647</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TCO</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2.5612</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TETCO-ELA</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3.042</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>3.042</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TETCO-M2 (receipts)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2.4175</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2.475</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TETCO-M3</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2.4926</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TETCO-STX</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2.7743</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>2.786</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2.786</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2.786</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TETCO-WLA</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2.9772</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>2.992</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TGP-500L</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4.3206</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>4.245</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>4.245</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>4.245</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TGP-800L</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2.932</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TGP-Z0</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TGP-Z1</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2.932</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TGP-Z4 200L</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2.5115</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2.685</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TGP-Z4 300L</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2.3724</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TGP-Z6 200L North</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TGP-Z6 200L South</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>2.581</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TGT (Zone 1)</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2.8203</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2.934</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2.934</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Transco-165</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>2.4926</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Transco-30</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>2.766</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2.766</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Transco-45</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>2.8382</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Transco-65</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>4.275</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4.3798</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Transco-85</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>4.4409</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>4.685</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Transco-Leidy</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>2.4509</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>2.571</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Transco-Z3</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>4.4409</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>3.975</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>3.975</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Transco-Z5</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>4.4485</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>4.346</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>4.346</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>4.346</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Transco-Z5 South</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>4.4485</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>4.577</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>4.577</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>4.577</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Transco-Z6  (non-NY)</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>2.4426</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Transco-Z6 (NY)</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>2.484</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Trunkline-Z1A</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>2.8253</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2.892</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2.892</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2.892</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Waha</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1.8123</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -9,7 +9,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$F$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$G$70</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -498,25 +499,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -529,13 +535,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3.035</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2.91</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>2.8799</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>2.9</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2.9</v>
@@ -543,6 +549,9 @@
       <c r="F2" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="G2" s="3" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -551,13 +560,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>2.6174</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>2.758</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>2.758</v>
@@ -565,6 +574,9 @@
       <c r="F3" s="3" t="n">
         <v>2.758</v>
       </c>
+      <c r="G3" s="3" t="n">
+        <v>2.758</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -573,13 +585,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>2.803</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>2.803</v>
@@ -587,6 +599,9 @@
       <c r="F4" s="3" t="n">
         <v>2.803</v>
       </c>
+      <c r="G4" s="3" t="n">
+        <v>2.803</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -595,13 +610,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>2.814</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>2.826</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2.826</v>
@@ -609,6 +624,9 @@
       <c r="F5" s="3" t="n">
         <v>2.826</v>
       </c>
+      <c r="G5" s="3" t="n">
+        <v>2.826</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -617,13 +635,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>2.8136</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>2.795</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>2.795</v>
@@ -631,6 +649,9 @@
       <c r="F6" s="3" t="n">
         <v>2.795</v>
       </c>
+      <c r="G6" s="3" t="n">
+        <v>2.795</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -639,13 +660,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>2.165</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.935</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>1.815</v>
@@ -653,6 +674,9 @@
       <c r="F7" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="G7" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -661,13 +685,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>1.958</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>1.815</v>
@@ -675,6 +699,9 @@
       <c r="F8" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="G8" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -683,13 +710,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2.7246</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>2.83</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2.83</v>
@@ -697,6 +724,9 @@
       <c r="F9" s="3" t="n">
         <v>2.83</v>
       </c>
+      <c r="G9" s="3" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -705,13 +735,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2.8088</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>2.78</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>2.78</v>
@@ -719,6 +749,9 @@
       <c r="F10" s="3" t="n">
         <v>2.78</v>
       </c>
+      <c r="G10" s="3" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -727,13 +760,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1.7466</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>1.204</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.204</v>
@@ -741,6 +774,9 @@
       <c r="F11" s="3" t="n">
         <v>1.204</v>
       </c>
+      <c r="G11" s="3" t="n">
+        <v>1.204</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -749,13 +785,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>2.425</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>2.4222</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>2.485</v>
@@ -763,6 +799,9 @@
       <c r="F12" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="G12" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -771,13 +810,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>2.8214</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>2.832</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.832</v>
@@ -785,6 +824,9 @@
       <c r="F13" s="3" t="n">
         <v>2.832</v>
       </c>
+      <c r="G13" s="3" t="n">
+        <v>2.832</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -793,13 +835,13 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>2.735</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>2.805</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>2.8</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>2.8</v>
@@ -807,6 +849,9 @@
       <c r="F14" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="G14" s="3" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -815,13 +860,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>3.555</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>4.48</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>4.5909</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>4.545</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>4.545</v>
@@ -829,6 +874,9 @@
       <c r="F15" s="3" t="n">
         <v>4.545</v>
       </c>
+      <c r="G15" s="3" t="n">
+        <v>4.545</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -837,13 +885,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>2.7991</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>2.55</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>2.55</v>
@@ -851,6 +899,9 @@
       <c r="F16" s="3" t="n">
         <v>2.55</v>
       </c>
+      <c r="G16" s="3" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -859,13 +910,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>3.215</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>3.2871</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>3.285</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>3.285</v>
@@ -873,6 +924,9 @@
       <c r="F17" s="3" t="n">
         <v>3.285</v>
       </c>
+      <c r="G17" s="3" t="n">
+        <v>3.285</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -881,13 +935,13 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>2.69</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>2.799</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>2.59</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>2.59</v>
@@ -895,6 +949,9 @@
       <c r="F18" s="3" t="n">
         <v>2.59</v>
       </c>
+      <c r="G18" s="3" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -903,13 +960,13 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>2.8072</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>2.5835</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>2.5835</v>
@@ -917,6 +974,9 @@
       <c r="F19" s="3" t="n">
         <v>2.5835</v>
       </c>
+      <c r="G19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -925,13 +985,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>2.745</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>2.788</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>2.5755</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>2.5755</v>
@@ -939,6 +999,9 @@
       <c r="F20" s="3" t="n">
         <v>2.5755</v>
       </c>
+      <c r="G20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -947,13 +1010,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>2.375</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>2.156</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>2.156</v>
@@ -961,6 +1024,9 @@
       <c r="F21" s="3" t="n">
         <v>2.156</v>
       </c>
+      <c r="G21" s="3" t="n">
+        <v>2.156</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -969,13 +1035,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>2.8098</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>2.866</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>2.866</v>
@@ -983,6 +1049,9 @@
       <c r="F22" s="3" t="n">
         <v>2.866</v>
       </c>
+      <c r="G22" s="3" t="n">
+        <v>2.866</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -991,13 +1060,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>2.35</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>2.525</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>2.525</v>
@@ -1005,6 +1074,9 @@
       <c r="F23" s="3" t="n">
         <v>2.525</v>
       </c>
+      <c r="G23" s="3" t="n">
+        <v>2.525</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1013,13 +1085,13 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>2.665</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>2.6798</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>2.781</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>2.781</v>
@@ -1027,6 +1099,9 @@
       <c r="F24" s="3" t="n">
         <v>2.781</v>
       </c>
+      <c r="G24" s="3" t="n">
+        <v>2.781</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1035,13 +1110,13 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>2.7689</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>2.81</v>
@@ -1049,6 +1124,9 @@
       <c r="F25" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="G25" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1057,13 +1135,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>2.7496</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>2.81</v>
@@ -1071,6 +1149,9 @@
       <c r="F26" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="G26" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1079,13 +1160,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>2.662</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>2.79</v>
@@ -1093,6 +1174,9 @@
       <c r="F27" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="G27" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1101,13 +1185,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>2.73</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>2.6808</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>2.84</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>2.84</v>
@@ -1115,6 +1199,9 @@
       <c r="F28" s="3" t="n">
         <v>2.84</v>
       </c>
+      <c r="G28" s="3" t="n">
+        <v>2.84</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1123,13 +1210,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>2.05</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>1.99</v>
@@ -1137,6 +1224,9 @@
       <c r="F29" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="G29" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1145,10 +1235,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>1.245</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1.572</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1.572</v>
@@ -1159,6 +1249,9 @@
       <c r="F30" s="3" t="n">
         <v>1.572</v>
       </c>
+      <c r="G30" s="3" t="n">
+        <v>1.572</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1167,13 +1260,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>2.6526</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>2.6865</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>2.6865</v>
@@ -1181,6 +1274,9 @@
       <c r="F31" s="3" t="n">
         <v>2.6865</v>
       </c>
+      <c r="G31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1189,13 +1285,13 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>2.075</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>1.9591</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>1.99</v>
@@ -1203,6 +1299,9 @@
       <c r="F32" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="G32" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1211,13 +1310,13 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>1.495</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1.3192</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>1.34</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>1.34</v>
@@ -1225,6 +1324,9 @@
       <c r="F33" s="3" t="n">
         <v>1.34</v>
       </c>
+      <c r="G33" s="3" t="n">
+        <v>1.34</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1233,13 +1335,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>2.6338</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.71</v>
@@ -1247,6 +1349,9 @@
       <c r="F34" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="G34" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1255,13 +1360,13 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1.7958</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>1.38</v>
@@ -1269,6 +1374,9 @@
       <c r="F35" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="G35" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1277,13 +1385,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>2.9677</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.992</v>
@@ -1291,6 +1399,9 @@
       <c r="F36" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="G36" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1299,13 +1410,13 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>2.725</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>2.7289</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>2.785</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>2.785</v>
@@ -1313,6 +1424,9 @@
       <c r="F37" s="3" t="n">
         <v>2.785</v>
       </c>
+      <c r="G37" s="3" t="n">
+        <v>2.785</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1321,13 +1435,13 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>2.255</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>2.007</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>2.135</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>2.135</v>
@@ -1335,6 +1449,9 @@
       <c r="F38" s="3" t="n">
         <v>2.135</v>
       </c>
+      <c r="G38" s="3" t="n">
+        <v>2.135</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1343,13 +1460,13 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>2.5482</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>2.485</v>
@@ -1357,6 +1474,9 @@
       <c r="F39" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="G39" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1365,13 +1485,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>3.29</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>3.2201</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>3.375</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>3.375</v>
@@ -1379,6 +1499,9 @@
       <c r="F40" s="3" t="n">
         <v>3.375</v>
       </c>
+      <c r="G40" s="3" t="n">
+        <v>3.375</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1387,13 +1510,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>4.315</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>4.4174</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>4.363</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>4.363</v>
@@ -1401,6 +1524,9 @@
       <c r="F41" s="3" t="n">
         <v>4.363</v>
       </c>
+      <c r="G41" s="3" t="n">
+        <v>4.363</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1409,13 +1535,13 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2.615</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2.6647</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>2.71</v>
@@ -1423,6 +1549,9 @@
       <c r="F42" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="G42" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1431,13 +1560,13 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>2.5612</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>2.6805</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>2.6805</v>
@@ -1445,6 +1574,9 @@
       <c r="F43" s="3" t="n">
         <v>2.6805</v>
       </c>
+      <c r="G43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1453,13 +1585,13 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>2.915</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>3.042</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>3.042</v>
@@ -1467,6 +1599,9 @@
       <c r="F44" s="3" t="n">
         <v>3.042</v>
       </c>
+      <c r="G44" s="3" t="n">
+        <v>3.042</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1475,13 +1610,13 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>2.4175</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>2.475</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>2.475</v>
@@ -1489,6 +1624,9 @@
       <c r="F45" s="3" t="n">
         <v>2.475</v>
       </c>
+      <c r="G45" s="3" t="n">
+        <v>2.475</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1497,13 +1635,13 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>2.48</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>2.48</v>
@@ -1511,6 +1649,9 @@
       <c r="F46" s="3" t="n">
         <v>2.48</v>
       </c>
+      <c r="G46" s="3" t="n">
+        <v>2.48</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1519,13 +1660,13 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>2.835</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>2.7743</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>2.786</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>2.786</v>
@@ -1533,6 +1674,9 @@
       <c r="F47" s="3" t="n">
         <v>2.786</v>
       </c>
+      <c r="G47" s="3" t="n">
+        <v>2.786</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1541,13 +1685,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>2.905</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>2.9772</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.992</v>
@@ -1555,6 +1699,9 @@
       <c r="F48" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="G48" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1563,13 +1710,13 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>4.295</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>4.3206</v>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>4.245</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>4.245</v>
@@ -1577,6 +1724,9 @@
       <c r="F49" s="3" t="n">
         <v>4.245</v>
       </c>
+      <c r="G49" s="3" t="n">
+        <v>4.245</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1585,13 +1735,13 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>2.845</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>2.795</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>2.932</v>
@@ -1599,6 +1749,9 @@
       <c r="F50" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="G50" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1607,13 +1760,13 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>2.768</v>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>2.79</v>
@@ -1621,6 +1774,9 @@
       <c r="F51" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="G51" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1629,10 +1785,10 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>2.785</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>2.76</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>2.932</v>
@@ -1643,6 +1799,9 @@
       <c r="F52" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="G52" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1651,13 +1810,13 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>2.5115</v>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>2.685</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2.685</v>
@@ -1665,6 +1824,9 @@
       <c r="F53" s="3" t="n">
         <v>2.685</v>
       </c>
+      <c r="G53" s="3" t="n">
+        <v>2.685</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1673,13 +1835,13 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>2.405</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>2.3724</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>2.4125</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>2.4125</v>
@@ -1687,6 +1849,9 @@
       <c r="F54" s="3" t="n">
         <v>2.4125</v>
       </c>
+      <c r="G54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1695,13 +1860,13 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>2.6755</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>2.6755</v>
@@ -1709,6 +1874,9 @@
       <c r="F55" s="3" t="n">
         <v>2.6755</v>
       </c>
+      <c r="G55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1717,13 +1885,13 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>2.581</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>2.581</v>
@@ -1731,6 +1899,9 @@
       <c r="F56" s="3" t="n">
         <v>2.581</v>
       </c>
+      <c r="G56" s="3" t="n">
+        <v>2.581</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1739,13 +1910,13 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>2.825</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>2.8203</v>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>2.934</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>2.934</v>
@@ -1753,6 +1924,9 @@
       <c r="F57" s="3" t="n">
         <v>2.934</v>
       </c>
+      <c r="G57" s="3" t="n">
+        <v>2.934</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1761,13 +1935,13 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>2.36</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>2.36</v>
@@ -1775,6 +1949,9 @@
       <c r="F58" s="3" t="n">
         <v>2.36</v>
       </c>
+      <c r="G58" s="3" t="n">
+        <v>2.36</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1783,13 +1960,13 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>2.83</v>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>2.766</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>2.766</v>
@@ -1797,6 +1974,9 @@
       <c r="F59" s="3" t="n">
         <v>2.766</v>
       </c>
+      <c r="G59" s="3" t="n">
+        <v>2.766</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1805,13 +1985,13 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>2.835</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>2.8382</v>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>3.0545</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>3.0545</v>
@@ -1819,6 +1999,9 @@
       <c r="F60" s="3" t="n">
         <v>3.0545</v>
       </c>
+      <c r="G60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1827,13 +2010,13 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>4.275</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>4.3798</v>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>3.95</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>3.95</v>
@@ -1841,6 +2024,9 @@
       <c r="F61" s="3" t="n">
         <v>3.95</v>
       </c>
+      <c r="G61" s="3" t="n">
+        <v>3.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1849,13 +2035,13 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="D62" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>4.685</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>4.685</v>
@@ -1863,6 +2049,9 @@
       <c r="F62" s="3" t="n">
         <v>4.685</v>
       </c>
+      <c r="G62" s="3" t="n">
+        <v>4.685</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1871,13 +2060,13 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>2.485</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="D63" s="3" t="n">
         <v>2.4509</v>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>2.571</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>2.571</v>
@@ -1885,6 +2074,9 @@
       <c r="F63" s="3" t="n">
         <v>2.571</v>
       </c>
+      <c r="G63" s="3" t="n">
+        <v>2.571</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1893,13 +2085,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="C64" s="3" t="n">
         <v>3.555</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="D64" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>3.975</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>3.975</v>
@@ -1907,6 +2099,9 @@
       <c r="F64" s="3" t="n">
         <v>3.975</v>
       </c>
+      <c r="G64" s="3" t="n">
+        <v>3.975</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1915,13 +2110,13 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="C65" s="3" t="n">
         <v>3.78</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="D65" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>4.346</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>4.346</v>
@@ -1929,6 +2124,9 @@
       <c r="F65" s="3" t="n">
         <v>4.346</v>
       </c>
+      <c r="G65" s="3" t="n">
+        <v>4.346</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1937,13 +2135,13 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="C66" s="3" t="n">
         <v>4.36</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="D66" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>4.577</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>4.577</v>
@@ -1951,6 +2149,9 @@
       <c r="F66" s="3" t="n">
         <v>4.577</v>
       </c>
+      <c r="G66" s="3" t="n">
+        <v>4.577</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1959,13 +2160,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="D67" s="3" t="n">
         <v>2.4426</v>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>2.4315</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>2.4315</v>
@@ -1973,6 +2174,9 @@
       <c r="F67" s="3" t="n">
         <v>2.4315</v>
       </c>
+      <c r="G67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1981,13 +2185,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>2.5</v>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>2.484</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>2.484</v>
@@ -1995,6 +2199,9 @@
       <c r="F68" s="3" t="n">
         <v>2.484</v>
       </c>
+      <c r="G68" s="3" t="n">
+        <v>2.484</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2003,13 +2210,13 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="C69" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="D69" s="3" t="n">
         <v>2.8253</v>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>2.892</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>2.892</v>
@@ -2017,6 +2224,9 @@
       <c r="F69" s="3" t="n">
         <v>2.892</v>
       </c>
+      <c r="G69" s="3" t="n">
+        <v>2.892</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2025,13 +2235,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="C70" s="3" t="n">
         <v>1.495</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="D70" s="3" t="n">
         <v>1.8123</v>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>1.38</v>
@@ -2039,9 +2249,12 @@
       <c r="F70" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="G70" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F70"/>
+  <autoFilter ref="A1:G70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -482,7 +482,7 @@
   <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>

--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -9,7 +9,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$H$70</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -489,6 +489,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -499,30 +500,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -535,16 +541,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2.915</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3.035</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>2.91</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>2.8799</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>2.9</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>2.9</v>
@@ -552,6 +558,9 @@
       <c r="G2" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="H2" s="3" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -560,16 +569,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2.46</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>2.6174</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2.758</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2.758</v>
@@ -577,6 +586,9 @@
       <c r="G3" s="3" t="n">
         <v>2.758</v>
       </c>
+      <c r="H3" s="3" t="n">
+        <v>2.758</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -585,16 +597,16 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2.175</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2.803</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>2.803</v>
@@ -602,6 +614,9 @@
       <c r="G4" s="3" t="n">
         <v>2.803</v>
       </c>
+      <c r="H4" s="3" t="n">
+        <v>2.803</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -610,16 +625,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>2.814</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>2.826</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>2.826</v>
@@ -627,6 +642,9 @@
       <c r="G5" s="3" t="n">
         <v>2.826</v>
       </c>
+      <c r="H5" s="3" t="n">
+        <v>2.826</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -635,16 +653,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>2.965</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>2.8136</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>2.795</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>2.795</v>
@@ -652,6 +670,9 @@
       <c r="G6" s="3" t="n">
         <v>2.795</v>
       </c>
+      <c r="H6" s="3" t="n">
+        <v>2.795</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -660,16 +681,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>2.165</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>1.935</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1.815</v>
@@ -677,6 +698,9 @@
       <c r="G7" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="H7" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -685,16 +709,16 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>1.958</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1.815</v>
@@ -702,6 +726,9 @@
       <c r="G8" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="H8" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -710,16 +737,16 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>2.635</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>2.7246</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>2.83</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>2.83</v>
@@ -727,6 +754,9 @@
       <c r="G9" s="3" t="n">
         <v>2.83</v>
       </c>
+      <c r="H9" s="3" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -735,16 +765,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>2.575</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>2.8088</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>2.78</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.78</v>
@@ -752,6 +782,9 @@
       <c r="G10" s="3" t="n">
         <v>2.78</v>
       </c>
+      <c r="H10" s="3" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -760,16 +793,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-1.045</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-1.8</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>1.7466</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>1.204</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1.204</v>
@@ -777,6 +810,9 @@
       <c r="G11" s="3" t="n">
         <v>1.204</v>
       </c>
+      <c r="H11" s="3" t="n">
+        <v>1.204</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -785,16 +821,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>2.06</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>2.425</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>2.4222</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>2.485</v>
@@ -802,6 +838,9 @@
       <c r="G12" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="H12" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -810,16 +849,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>2.73</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>2.8214</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>2.832</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>2.832</v>
@@ -827,6 +866,9 @@
       <c r="G13" s="3" t="n">
         <v>2.832</v>
       </c>
+      <c r="H13" s="3" t="n">
+        <v>2.832</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -835,16 +877,16 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>2.535</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>2.735</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>2.805</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>2.8</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>2.8</v>
@@ -852,6 +894,9 @@
       <c r="G14" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="H14" s="3" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -860,16 +905,16 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>3.555</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>4.48</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>4.5909</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>4.545</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>4.545</v>
@@ -877,6 +922,9 @@
       <c r="G15" s="3" t="n">
         <v>4.545</v>
       </c>
+      <c r="H15" s="3" t="n">
+        <v>4.545</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -885,16 +933,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>2.835</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>2.7991</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>2.55</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>2.55</v>
@@ -902,6 +950,9 @@
       <c r="G16" s="3" t="n">
         <v>2.55</v>
       </c>
+      <c r="H16" s="3" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -910,16 +961,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>3.075</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>3.34</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>3.215</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>3.2871</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>3.285</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>3.285</v>
@@ -927,6 +978,9 @@
       <c r="G17" s="3" t="n">
         <v>3.285</v>
       </c>
+      <c r="H17" s="3" t="n">
+        <v>3.285</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -935,16 +989,16 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>2.69</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>2.799</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>2.59</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>2.59</v>
@@ -952,6 +1006,9 @@
       <c r="G18" s="3" t="n">
         <v>2.59</v>
       </c>
+      <c r="H18" s="3" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -960,16 +1017,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>2.455</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>2.8072</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>2.5835</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>2.5835</v>
@@ -977,6 +1034,9 @@
       <c r="G19" s="3" t="n">
         <v>2.5835</v>
       </c>
+      <c r="H19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -985,16 +1045,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>2.81</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>2.745</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>2.788</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>2.5755</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>2.5755</v>
@@ -1002,6 +1062,9 @@
       <c r="G20" s="3" t="n">
         <v>2.5755</v>
       </c>
+      <c r="H20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1010,16 +1073,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>2.375</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>2.156</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>2.156</v>
@@ -1027,6 +1090,9 @@
       <c r="G21" s="3" t="n">
         <v>2.156</v>
       </c>
+      <c r="H21" s="3" t="n">
+        <v>2.156</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1035,16 +1101,16 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>2.8098</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>2.866</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>2.866</v>
@@ -1052,6 +1118,9 @@
       <c r="G22" s="3" t="n">
         <v>2.866</v>
       </c>
+      <c r="H22" s="3" t="n">
+        <v>2.866</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1060,16 +1129,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>1.97</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>2.35</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>2.525</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>2.525</v>
@@ -1077,6 +1146,9 @@
       <c r="G23" s="3" t="n">
         <v>2.525</v>
       </c>
+      <c r="H23" s="3" t="n">
+        <v>2.525</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1085,16 +1157,16 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>2.63</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>2.665</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>2.6798</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>2.781</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>2.781</v>
@@ -1102,6 +1174,9 @@
       <c r="G24" s="3" t="n">
         <v>2.781</v>
       </c>
+      <c r="H24" s="3" t="n">
+        <v>2.781</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1110,16 +1185,16 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>2.7689</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>2.81</v>
@@ -1127,6 +1202,9 @@
       <c r="G25" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="H25" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1135,16 +1213,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>2.7496</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>2.81</v>
@@ -1152,6 +1230,9 @@
       <c r="G26" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="H26" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1160,16 +1241,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>2.275</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>2.662</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>2.79</v>
@@ -1177,6 +1258,9 @@
       <c r="G27" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="H27" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1185,16 +1269,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>2.565</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>2.73</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>2.6808</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>2.84</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>2.84</v>
@@ -1202,6 +1286,9 @@
       <c r="G28" s="3" t="n">
         <v>2.84</v>
       </c>
+      <c r="H28" s="3" t="n">
+        <v>2.84</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1210,16 +1297,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>2.05</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>1.99</v>
@@ -1227,6 +1314,9 @@
       <c r="G29" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="H29" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1235,13 +1325,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>1.245</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>1.572</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1.572</v>
@@ -1252,6 +1342,9 @@
       <c r="G30" s="3" t="n">
         <v>1.572</v>
       </c>
+      <c r="H30" s="3" t="n">
+        <v>1.572</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1260,16 +1353,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>2.655</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>2.6526</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>2.6865</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>2.6865</v>
@@ -1277,6 +1370,9 @@
       <c r="G31" s="3" t="n">
         <v>2.6865</v>
       </c>
+      <c r="H31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1285,16 +1381,16 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>1.715</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>1.81</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>2.075</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>1.9591</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>1.99</v>
@@ -1302,6 +1398,9 @@
       <c r="G32" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="H32" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1310,16 +1409,16 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>1.495</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>1.3192</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>1.34</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>1.34</v>
@@ -1327,6 +1426,9 @@
       <c r="G33" s="3" t="n">
         <v>1.34</v>
       </c>
+      <c r="H33" s="3" t="n">
+        <v>1.34</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1335,16 +1437,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>2.6338</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2.71</v>
@@ -1352,6 +1454,9 @@
       <c r="G34" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="H34" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1360,16 +1465,16 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-1.045</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-1.8</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>1.7958</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>1.38</v>
@@ -1377,6 +1482,9 @@
       <c r="G35" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="H35" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1385,16 +1493,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>3.03</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>2.9677</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>2.992</v>
@@ -1402,6 +1510,9 @@
       <c r="G36" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="H36" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1410,16 +1521,16 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>2.605</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>2.725</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>2.7289</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>2.785</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>2.785</v>
@@ -1427,6 +1538,9 @@
       <c r="G37" s="3" t="n">
         <v>2.785</v>
       </c>
+      <c r="H37" s="3" t="n">
+        <v>2.785</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1435,16 +1549,16 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>2.255</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>2.007</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>2.135</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>2.135</v>
@@ -1452,6 +1566,9 @@
       <c r="G38" s="3" t="n">
         <v>2.135</v>
       </c>
+      <c r="H38" s="3" t="n">
+        <v>2.135</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1460,16 +1577,16 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>1.415</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>2.5482</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>2.485</v>
@@ -1477,6 +1594,9 @@
       <c r="G39" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="H39" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1485,16 +1605,16 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>2.505</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>3.29</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>3.2201</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>3.375</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>3.375</v>
@@ -1502,6 +1622,9 @@
       <c r="G40" s="3" t="n">
         <v>3.375</v>
       </c>
+      <c r="H40" s="3" t="n">
+        <v>3.375</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1510,16 +1633,16 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>3.41</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>4.315</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>4.4174</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>4.363</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>4.363</v>
@@ -1527,6 +1650,9 @@
       <c r="G41" s="3" t="n">
         <v>4.363</v>
       </c>
+      <c r="H41" s="3" t="n">
+        <v>4.363</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1535,16 +1661,16 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>2.545</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>2.615</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>2.6647</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>2.71</v>
@@ -1552,6 +1678,9 @@
       <c r="G42" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="H42" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1560,16 +1689,16 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>2.17</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>2.5612</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>2.6805</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>2.6805</v>
@@ -1577,6 +1706,9 @@
       <c r="G43" s="3" t="n">
         <v>2.6805</v>
       </c>
+      <c r="H43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1585,16 +1717,16 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>2.99</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>2.915</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>3.042</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>3.042</v>
@@ -1602,6 +1734,9 @@
       <c r="G44" s="3" t="n">
         <v>3.042</v>
       </c>
+      <c r="H44" s="3" t="n">
+        <v>3.042</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1610,16 +1745,16 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>2.045</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>2.4175</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>2.475</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>2.475</v>
@@ -1627,6 +1762,9 @@
       <c r="G45" s="3" t="n">
         <v>2.475</v>
       </c>
+      <c r="H45" s="3" t="n">
+        <v>2.475</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1635,16 +1773,16 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>2.48</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>2.48</v>
@@ -1652,6 +1790,9 @@
       <c r="G46" s="3" t="n">
         <v>2.48</v>
       </c>
+      <c r="H46" s="3" t="n">
+        <v>2.48</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1660,16 +1801,16 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>2.835</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>2.7743</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>2.786</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>2.786</v>
@@ -1677,6 +1818,9 @@
       <c r="G47" s="3" t="n">
         <v>2.786</v>
       </c>
+      <c r="H47" s="3" t="n">
+        <v>2.786</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1685,16 +1829,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>3.03</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>2.905</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>2.9772</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>2.992</v>
@@ -1702,6 +1846,9 @@
       <c r="G48" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="H48" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1710,16 +1857,16 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>3.39</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>4.295</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>4.3206</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>4.245</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>4.245</v>
@@ -1727,6 +1874,9 @@
       <c r="G49" s="3" t="n">
         <v>4.245</v>
       </c>
+      <c r="H49" s="3" t="n">
+        <v>4.245</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1735,16 +1885,16 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>2.845</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>2.795</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>2.932</v>
@@ -1752,6 +1902,9 @@
       <c r="G50" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="H50" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1760,16 +1913,16 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>2.768</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>2.79</v>
@@ -1777,6 +1930,9 @@
       <c r="G51" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="H51" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1785,13 +1941,13 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>2.785</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>2.76</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>2.932</v>
@@ -1802,6 +1958,9 @@
       <c r="G52" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="H52" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1810,16 +1969,16 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>2.07</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>2.5115</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>2.685</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>2.685</v>
@@ -1827,6 +1986,9 @@
       <c r="G53" s="3" t="n">
         <v>2.685</v>
       </c>
+      <c r="H53" s="3" t="n">
+        <v>2.685</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1835,16 +1997,16 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>1.875</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>2.405</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>2.3724</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>2.4125</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>2.4125</v>
@@ -1852,6 +2014,9 @@
       <c r="G54" s="3" t="n">
         <v>2.4125</v>
       </c>
+      <c r="H54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1860,16 +2025,16 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>2.365</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>2.6755</v>
       </c>
       <c r="F55" s="3" t="n">
         <v>2.6755</v>
@@ -1877,6 +2042,9 @@
       <c r="G55" s="3" t="n">
         <v>2.6755</v>
       </c>
+      <c r="H55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1885,16 +2053,16 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>2.185</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>2.581</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>2.581</v>
@@ -1902,6 +2070,9 @@
       <c r="G56" s="3" t="n">
         <v>2.581</v>
       </c>
+      <c r="H56" s="3" t="n">
+        <v>2.581</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1910,16 +2081,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>2.825</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>2.8203</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>2.934</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>2.934</v>
@@ -1927,6 +2098,9 @@
       <c r="G57" s="3" t="n">
         <v>2.934</v>
       </c>
+      <c r="H57" s="3" t="n">
+        <v>2.934</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1935,16 +2109,16 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>2.36</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>2.36</v>
@@ -1952,6 +2126,9 @@
       <c r="G58" s="3" t="n">
         <v>2.36</v>
       </c>
+      <c r="H58" s="3" t="n">
+        <v>2.36</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1960,16 +2137,16 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>2.505</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>2.755</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E59" s="3" t="n">
         <v>2.83</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>2.766</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>2.766</v>
@@ -1977,6 +2154,9 @@
       <c r="G59" s="3" t="n">
         <v>2.766</v>
       </c>
+      <c r="H59" s="3" t="n">
+        <v>2.766</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1985,16 +2165,16 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>2.835</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>2.8382</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>3.0545</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>3.0545</v>
@@ -2002,6 +2182,9 @@
       <c r="G60" s="3" t="n">
         <v>3.0545</v>
       </c>
+      <c r="H60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2010,16 +2193,16 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C61" s="3" t="n">
         <v>3.38</v>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="D61" s="3" t="n">
         <v>4.275</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="3" t="n">
         <v>4.3798</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>3.95</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>3.95</v>
@@ -2027,6 +2210,9 @@
       <c r="G61" s="3" t="n">
         <v>3.95</v>
       </c>
+      <c r="H61" s="3" t="n">
+        <v>3.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2035,16 +2221,16 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="C62" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="D62" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="E62" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>4.685</v>
       </c>
       <c r="F62" s="3" t="n">
         <v>4.685</v>
@@ -2052,6 +2238,9 @@
       <c r="G62" s="3" t="n">
         <v>4.685</v>
       </c>
+      <c r="H62" s="3" t="n">
+        <v>4.685</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2060,16 +2249,16 @@
         </is>
       </c>
       <c r="B63" s="3" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="C63" s="3" t="n">
         <v>2.06</v>
       </c>
-      <c r="C63" s="3" t="n">
+      <c r="D63" s="3" t="n">
         <v>2.485</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="E63" s="3" t="n">
         <v>2.4509</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>2.571</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>2.571</v>
@@ -2077,6 +2266,9 @@
       <c r="G63" s="3" t="n">
         <v>2.571</v>
       </c>
+      <c r="H63" s="3" t="n">
+        <v>2.571</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2085,16 +2277,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="C64" s="3" t="n">
         <v>3.31</v>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="D64" s="3" t="n">
         <v>3.555</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="E64" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>3.975</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>3.975</v>
@@ -2102,6 +2294,9 @@
       <c r="G64" s="3" t="n">
         <v>3.975</v>
       </c>
+      <c r="H64" s="3" t="n">
+        <v>3.975</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2110,16 +2305,16 @@
         </is>
       </c>
       <c r="B65" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C65" s="3" t="n">
         <v>2.66</v>
       </c>
-      <c r="C65" s="3" t="n">
+      <c r="D65" s="3" t="n">
         <v>3.78</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="E65" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>4.346</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>4.346</v>
@@ -2127,6 +2322,9 @@
       <c r="G65" s="3" t="n">
         <v>4.346</v>
       </c>
+      <c r="H65" s="3" t="n">
+        <v>4.346</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2135,16 +2333,16 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C66" s="3" t="n">
         <v>3.425</v>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="D66" s="3" t="n">
         <v>4.36</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="E66" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>4.577</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>4.577</v>
@@ -2152,6 +2350,9 @@
       <c r="G66" s="3" t="n">
         <v>4.577</v>
       </c>
+      <c r="H66" s="3" t="n">
+        <v>4.577</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2160,16 +2361,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="C67" s="3" t="n">
         <v>2.075</v>
       </c>
-      <c r="C67" s="3" t="n">
+      <c r="D67" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="E67" s="3" t="n">
         <v>2.4426</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>2.4315</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>2.4315</v>
@@ -2177,6 +2378,9 @@
       <c r="G67" s="3" t="n">
         <v>2.4315</v>
       </c>
+      <c r="H67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2185,16 +2389,16 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="E68" s="3" t="n">
         <v>2.5</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>2.484</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>2.484</v>
@@ -2202,6 +2406,9 @@
       <c r="G68" s="3" t="n">
         <v>2.484</v>
       </c>
+      <c r="H68" s="3" t="n">
+        <v>2.484</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2210,16 +2417,16 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
+        <v>2.545</v>
+      </c>
+      <c r="C69" s="3" t="n">
         <v>2.745</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="D69" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="E69" s="3" t="n">
         <v>2.8253</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>2.892</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>2.892</v>
@@ -2227,6 +2434,9 @@
       <c r="G69" s="3" t="n">
         <v>2.892</v>
       </c>
+      <c r="H69" s="3" t="n">
+        <v>2.892</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2235,16 +2445,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C70" s="3" t="n">
         <v>-1.78</v>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="D70" s="3" t="n">
         <v>1.495</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="E70" s="3" t="n">
         <v>1.8123</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>1.38</v>
@@ -2252,9 +2462,12 @@
       <c r="G70" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="H70" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:H70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -9,7 +9,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$H$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$I$70</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -490,6 +490,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -510,25 +511,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -547,13 +553,13 @@
         <v>3.035</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>2.8483</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>2.91</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2.8799</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>2.9</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2.9</v>
@@ -561,6 +567,9 @@
       <c r="H2" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="I2" s="3" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -575,13 +584,13 @@
         <v>2.46</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>2.2683</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>2.6174</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2.758</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>2.758</v>
@@ -589,6 +598,9 @@
       <c r="H3" s="3" t="n">
         <v>2.758</v>
       </c>
+      <c r="I3" s="3" t="n">
+        <v>2.758</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -603,13 +615,13 @@
         <v>2.175</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2.803</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2.803</v>
@@ -617,6 +629,9 @@
       <c r="H4" s="3" t="n">
         <v>2.803</v>
       </c>
+      <c r="I4" s="3" t="n">
+        <v>2.803</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -631,13 +646,13 @@
         <v>2.8</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>2.7135</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>2.814</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>2.826</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2.826</v>
@@ -645,6 +660,9 @@
       <c r="H5" s="3" t="n">
         <v>2.826</v>
       </c>
+      <c r="I5" s="3" t="n">
+        <v>2.826</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -659,13 +677,13 @@
         <v>2.965</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>2.8395</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>2.8136</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>2.795</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>2.795</v>
@@ -673,6 +691,9 @@
       <c r="H6" s="3" t="n">
         <v>2.795</v>
       </c>
+      <c r="I6" s="3" t="n">
+        <v>2.795</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -687,13 +708,13 @@
         <v>1.5</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>1.3856</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>2.165</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>1.935</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1.815</v>
@@ -701,6 +722,9 @@
       <c r="H7" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="I7" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -715,13 +739,13 @@
         <v>1.5</v>
       </c>
       <c r="D8" s="3" t="n">
+        <v>1.4121</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1.958</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>1.815</v>
@@ -729,6 +753,9 @@
       <c r="H8" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="I8" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -743,13 +770,13 @@
         <v>2.635</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>2.6346</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>2.7246</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>2.83</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>2.83</v>
@@ -757,6 +784,9 @@
       <c r="H9" s="3" t="n">
         <v>2.83</v>
       </c>
+      <c r="I9" s="3" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -771,13 +801,13 @@
         <v>2.575</v>
       </c>
       <c r="D10" s="3" t="n">
+        <v>2.6033</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>2.8088</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>2.78</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2.78</v>
@@ -785,6 +815,9 @@
       <c r="H10" s="3" t="n">
         <v>2.78</v>
       </c>
+      <c r="I10" s="3" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -799,13 +832,13 @@
         <v>-1.8</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>-2.5212</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>1.7466</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>1.204</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>1.204</v>
@@ -813,6 +846,9 @@
       <c r="H11" s="3" t="n">
         <v>1.204</v>
       </c>
+      <c r="I11" s="3" t="n">
+        <v>1.204</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -827,13 +863,13 @@
         <v>2.06</v>
       </c>
       <c r="D12" s="3" t="n">
+        <v>1.8552</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>2.425</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>2.4222</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>2.485</v>
@@ -841,6 +877,9 @@
       <c r="H12" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="I12" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -855,13 +894,13 @@
         <v>2.73</v>
       </c>
       <c r="D13" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>2.8214</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>2.832</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>2.832</v>
@@ -869,6 +908,9 @@
       <c r="H13" s="3" t="n">
         <v>2.832</v>
       </c>
+      <c r="I13" s="3" t="n">
+        <v>2.832</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -883,13 +925,13 @@
         <v>2.535</v>
       </c>
       <c r="D14" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>2.735</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>2.805</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>2.8</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>2.8</v>
@@ -897,6 +939,9 @@
       <c r="H14" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="I14" s="3" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -911,13 +956,13 @@
         <v>3.555</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>3.4716</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>4.48</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>4.5909</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>4.545</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>4.545</v>
@@ -925,6 +970,9 @@
       <c r="H15" s="3" t="n">
         <v>4.545</v>
       </c>
+      <c r="I15" s="3" t="n">
+        <v>4.545</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -939,13 +987,13 @@
         <v>2.835</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>2.732</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>2.7991</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>2.55</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>2.55</v>
@@ -953,6 +1001,9 @@
       <c r="H16" s="3" t="n">
         <v>2.55</v>
       </c>
+      <c r="I16" s="3" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -967,13 +1018,13 @@
         <v>3.34</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>3.0859</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>3.215</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>3.2871</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>3.285</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>3.285</v>
@@ -981,6 +1032,9 @@
       <c r="H17" s="3" t="n">
         <v>3.285</v>
       </c>
+      <c r="I17" s="3" t="n">
+        <v>3.285</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -995,13 +1049,13 @@
         <v>2.45</v>
       </c>
       <c r="D18" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>2.69</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>2.799</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>2.59</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2.59</v>
@@ -1009,6 +1063,9 @@
       <c r="H18" s="3" t="n">
         <v>2.59</v>
       </c>
+      <c r="I18" s="3" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1023,13 +1080,13 @@
         <v>2.455</v>
       </c>
       <c r="D19" s="3" t="n">
+        <v>2.5163</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>2.8072</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>2.5835</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>2.5835</v>
@@ -1037,6 +1094,9 @@
       <c r="H19" s="3" t="n">
         <v>2.5835</v>
       </c>
+      <c r="I19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1051,13 +1111,13 @@
         <v>2.81</v>
       </c>
       <c r="D20" s="3" t="n">
+        <v>2.7234</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>2.745</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>2.788</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>2.5755</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>2.5755</v>
@@ -1065,6 +1125,9 @@
       <c r="H20" s="3" t="n">
         <v>2.5755</v>
       </c>
+      <c r="I20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1079,13 +1142,13 @@
         <v>1.54</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>1.3913</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>2.375</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2.156</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>2.156</v>
@@ -1093,6 +1156,9 @@
       <c r="H21" s="3" t="n">
         <v>2.156</v>
       </c>
+      <c r="I21" s="3" t="n">
+        <v>2.156</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1107,13 +1173,13 @@
         <v>2.5</v>
       </c>
       <c r="D22" s="3" t="n">
+        <v>2.5977</v>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>2.8098</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>2.866</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>2.866</v>
@@ -1121,6 +1187,9 @@
       <c r="H22" s="3" t="n">
         <v>2.866</v>
       </c>
+      <c r="I22" s="3" t="n">
+        <v>2.866</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1135,13 +1204,13 @@
         <v>1.97</v>
       </c>
       <c r="D23" s="3" t="n">
+        <v>1.8045</v>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>2.35</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>2.525</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>2.525</v>
@@ -1149,6 +1218,9 @@
       <c r="H23" s="3" t="n">
         <v>2.525</v>
       </c>
+      <c r="I23" s="3" t="n">
+        <v>2.525</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1163,13 +1235,13 @@
         <v>2.63</v>
       </c>
       <c r="D24" s="3" t="n">
+        <v>2.5842</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>2.665</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>2.6798</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>2.781</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>2.781</v>
@@ -1177,6 +1249,9 @@
       <c r="H24" s="3" t="n">
         <v>2.781</v>
       </c>
+      <c r="I24" s="3" t="n">
+        <v>2.781</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1191,13 +1266,13 @@
         <v>2.78</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v>2.6527</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>2.7689</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>2.81</v>
@@ -1205,6 +1280,9 @@
       <c r="H25" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="I25" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1219,13 +1297,13 @@
         <v>2.72</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v>2.6593</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>2.7496</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>2.81</v>
@@ -1233,6 +1311,9 @@
       <c r="H26" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="I26" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1247,13 +1328,13 @@
         <v>2.5</v>
       </c>
       <c r="D27" s="3" t="n">
+        <v>2.4697</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>2.662</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>2.79</v>
@@ -1261,6 +1342,9 @@
       <c r="H27" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="I27" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1275,13 +1359,13 @@
         <v>2.565</v>
       </c>
       <c r="D28" s="3" t="n">
+        <v>2.5291</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>2.73</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>2.6808</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>2.84</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>2.84</v>
@@ -1289,6 +1373,9 @@
       <c r="H28" s="3" t="n">
         <v>2.84</v>
       </c>
+      <c r="I28" s="3" t="n">
+        <v>2.84</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1303,13 +1390,13 @@
         <v>1.49</v>
       </c>
       <c r="D29" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>2.05</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>1.99</v>
@@ -1317,6 +1404,9 @@
       <c r="H29" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="I29" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1331,10 +1421,10 @@
         <v>1.45</v>
       </c>
       <c r="D30" s="3" t="n">
+        <v>1.244</v>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>1.245</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>1.572</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>1.572</v>
@@ -1345,6 +1435,9 @@
       <c r="H30" s="3" t="n">
         <v>1.572</v>
       </c>
+      <c r="I30" s="3" t="n">
+        <v>1.572</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1359,13 +1452,13 @@
         <v>2.655</v>
       </c>
       <c r="D31" s="3" t="n">
+        <v>2.3698</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>2.6526</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>2.6865</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>2.6865</v>
@@ -1373,6 +1466,9 @@
       <c r="H31" s="3" t="n">
         <v>2.6865</v>
       </c>
+      <c r="I31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1387,13 +1483,13 @@
         <v>1.81</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v>1.6327</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>2.075</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1.9591</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>1.99</v>
@@ -1401,6 +1497,9 @@
       <c r="H32" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="I32" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1415,13 +1514,13 @@
         <v>1.495</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>1.3703</v>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>1.3192</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1.34</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>1.34</v>
@@ -1429,6 +1528,9 @@
       <c r="H33" s="3" t="n">
         <v>1.34</v>
       </c>
+      <c r="I33" s="3" t="n">
+        <v>1.34</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1443,13 +1545,13 @@
         <v>2.5</v>
       </c>
       <c r="D34" s="3" t="n">
+        <v>2.3405</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>2.6338</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>2.71</v>
@@ -1457,6 +1559,9 @@
       <c r="H34" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="I34" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1471,13 +1576,13 @@
         <v>-1.8</v>
       </c>
       <c r="D35" s="3" t="n">
+        <v>-2.4215</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>1.7958</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>1.38</v>
@@ -1485,6 +1590,9 @@
       <c r="H35" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="I35" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1499,13 +1607,13 @@
         <v>3.03</v>
       </c>
       <c r="D36" s="3" t="n">
+        <v>2.8835</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>2.9677</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>2.992</v>
@@ -1513,6 +1621,9 @@
       <c r="H36" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="I36" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1527,13 +1638,13 @@
         <v>2.605</v>
       </c>
       <c r="D37" s="3" t="n">
+        <v>2.6377</v>
+      </c>
+      <c r="E37" s="3" t="n">
         <v>2.725</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>2.7289</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>2.785</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>2.785</v>
@@ -1541,6 +1652,9 @@
       <c r="H37" s="3" t="n">
         <v>2.785</v>
       </c>
+      <c r="I37" s="3" t="n">
+        <v>2.785</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1555,13 +1669,13 @@
         <v>1.4</v>
       </c>
       <c r="D38" s="3" t="n">
+        <v>1.2395</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>2.255</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>2.007</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>2.135</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>2.135</v>
@@ -1569,6 +1683,9 @@
       <c r="H38" s="3" t="n">
         <v>2.135</v>
       </c>
+      <c r="I38" s="3" t="n">
+        <v>2.135</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1583,13 +1700,13 @@
         <v>1.415</v>
       </c>
       <c r="D39" s="3" t="n">
+        <v>1.3731</v>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>2.5482</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>2.485</v>
@@ -1597,6 +1714,9 @@
       <c r="H39" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="I39" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1611,13 +1731,13 @@
         <v>2.505</v>
       </c>
       <c r="D40" s="3" t="n">
+        <v>2.4226</v>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>3.29</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>3.2201</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>3.375</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>3.375</v>
@@ -1625,6 +1745,9 @@
       <c r="H40" s="3" t="n">
         <v>3.375</v>
       </c>
+      <c r="I40" s="3" t="n">
+        <v>3.375</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1639,13 +1762,13 @@
         <v>3.41</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v>3.3317</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>4.315</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>4.4174</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>4.363</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>4.363</v>
@@ -1653,6 +1776,9 @@
       <c r="H41" s="3" t="n">
         <v>4.363</v>
       </c>
+      <c r="I41" s="3" t="n">
+        <v>4.363</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1667,13 +1793,13 @@
         <v>2.545</v>
       </c>
       <c r="D42" s="3" t="n">
+        <v>2.3954</v>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>2.615</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>2.6647</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>2.71</v>
@@ -1681,6 +1807,9 @@
       <c r="H42" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="I42" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1695,13 +1824,13 @@
         <v>2.17</v>
       </c>
       <c r="D43" s="3" t="n">
+        <v>1.9892</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>2.5612</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>2.6805</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>2.6805</v>
@@ -1709,6 +1838,9 @@
       <c r="H43" s="3" t="n">
         <v>2.6805</v>
       </c>
+      <c r="I43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1723,13 +1855,13 @@
         <v>2.99</v>
       </c>
       <c r="D44" s="3" t="n">
+        <v>2.8703</v>
+      </c>
+      <c r="E44" s="3" t="n">
         <v>2.915</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>3.042</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>3.042</v>
@@ -1737,6 +1869,9 @@
       <c r="H44" s="3" t="n">
         <v>3.042</v>
       </c>
+      <c r="I44" s="3" t="n">
+        <v>3.042</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1751,13 +1886,13 @@
         <v>2.045</v>
       </c>
       <c r="D45" s="3" t="n">
+        <v>1.8598</v>
+      </c>
+      <c r="E45" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>2.4175</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>2.475</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>2.475</v>
@@ -1765,6 +1900,9 @@
       <c r="H45" s="3" t="n">
         <v>2.475</v>
       </c>
+      <c r="I45" s="3" t="n">
+        <v>2.475</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1779,13 +1917,13 @@
         <v>2.09</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>1.9239</v>
+      </c>
+      <c r="E46" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>2.48</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>2.48</v>
@@ -1793,6 +1931,9 @@
       <c r="H46" s="3" t="n">
         <v>2.48</v>
       </c>
+      <c r="I46" s="3" t="n">
+        <v>2.48</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1807,13 +1948,13 @@
         <v>2.835</v>
       </c>
       <c r="D47" s="3" t="n">
+        <v>2.736</v>
+      </c>
+      <c r="E47" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>2.7743</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>2.786</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>2.786</v>
@@ -1821,6 +1962,9 @@
       <c r="H47" s="3" t="n">
         <v>2.786</v>
       </c>
+      <c r="I47" s="3" t="n">
+        <v>2.786</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1835,13 +1979,13 @@
         <v>3.03</v>
       </c>
       <c r="D48" s="3" t="n">
+        <v>2.8699</v>
+      </c>
+      <c r="E48" s="3" t="n">
         <v>2.905</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>2.9772</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.992</v>
@@ -1849,6 +1993,9 @@
       <c r="H48" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="I48" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1863,13 +2010,13 @@
         <v>3.39</v>
       </c>
       <c r="D49" s="3" t="n">
+        <v>3.3178</v>
+      </c>
+      <c r="E49" s="3" t="n">
         <v>4.295</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>4.3206</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>4.245</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>4.245</v>
@@ -1877,6 +2024,9 @@
       <c r="H49" s="3" t="n">
         <v>4.245</v>
       </c>
+      <c r="I49" s="3" t="n">
+        <v>4.245</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1891,13 +2041,13 @@
         <v>2.845</v>
       </c>
       <c r="D50" s="3" t="n">
+        <v>2.7533</v>
+      </c>
+      <c r="E50" s="3" t="n">
         <v>2.795</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="G50" s="3" t="n">
         <v>2.932</v>
@@ -1905,6 +2055,9 @@
       <c r="H50" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="I50" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1919,13 +2072,13 @@
         <v>2.78</v>
       </c>
       <c r="D51" s="3" t="n">
+        <v>2.6528</v>
+      </c>
+      <c r="E51" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>2.768</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>2.79</v>
@@ -1933,6 +2086,9 @@
       <c r="H51" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="I51" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1947,10 +2103,10 @@
         <v>2.785</v>
       </c>
       <c r="D52" s="3" t="n">
+        <v>2.699</v>
+      </c>
+      <c r="E52" s="3" t="n">
         <v>2.76</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>2.932</v>
@@ -1961,6 +2117,9 @@
       <c r="H52" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="I52" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1975,13 +2134,13 @@
         <v>2.07</v>
       </c>
       <c r="D53" s="3" t="n">
+        <v>1.9043</v>
+      </c>
+      <c r="E53" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>2.5115</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>2.685</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>2.685</v>
@@ -1989,6 +2148,9 @@
       <c r="H53" s="3" t="n">
         <v>2.685</v>
       </c>
+      <c r="I53" s="3" t="n">
+        <v>2.685</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2003,13 +2165,13 @@
         <v>1.875</v>
       </c>
       <c r="D54" s="3" t="n">
+        <v>1.7917</v>
+      </c>
+      <c r="E54" s="3" t="n">
         <v>2.405</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>2.3724</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2.4125</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>2.4125</v>
@@ -2017,6 +2179,9 @@
       <c r="H54" s="3" t="n">
         <v>2.4125</v>
       </c>
+      <c r="I54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2031,13 +2196,13 @@
         <v>2.365</v>
       </c>
       <c r="D55" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E55" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>2.6755</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>2.6755</v>
@@ -2045,6 +2210,9 @@
       <c r="H55" s="3" t="n">
         <v>2.6755</v>
       </c>
+      <c r="I55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2059,13 +2227,13 @@
         <v>2.185</v>
       </c>
       <c r="D56" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E56" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>2.581</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>2.581</v>
@@ -2073,6 +2241,9 @@
       <c r="H56" s="3" t="n">
         <v>2.581</v>
       </c>
+      <c r="I56" s="3" t="n">
+        <v>2.581</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2087,13 +2258,13 @@
         <v>2.8</v>
       </c>
       <c r="D57" s="3" t="n">
+        <v>2.7214</v>
+      </c>
+      <c r="E57" s="3" t="n">
         <v>2.825</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>2.8203</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>2.934</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>2.934</v>
@@ -2101,6 +2272,9 @@
       <c r="H57" s="3" t="n">
         <v>2.934</v>
       </c>
+      <c r="I57" s="3" t="n">
+        <v>2.934</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2115,13 +2289,13 @@
         <v>2.14</v>
       </c>
       <c r="D58" s="3" t="n">
+        <v>1.9239</v>
+      </c>
+      <c r="E58" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>2.36</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>2.36</v>
@@ -2129,6 +2303,9 @@
       <c r="H58" s="3" t="n">
         <v>2.36</v>
       </c>
+      <c r="I58" s="3" t="n">
+        <v>2.36</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2143,13 +2320,13 @@
         <v>2.755</v>
       </c>
       <c r="D59" s="3" t="n">
+        <v>2.4822</v>
+      </c>
+      <c r="E59" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>2.83</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>2.766</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>2.766</v>
@@ -2157,6 +2334,9 @@
       <c r="H59" s="3" t="n">
         <v>2.766</v>
       </c>
+      <c r="I59" s="3" t="n">
+        <v>2.766</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2171,13 +2351,13 @@
         <v>2.93</v>
       </c>
       <c r="D60" s="3" t="n">
+        <v>2.8109</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>2.835</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>2.8382</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>3.0545</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>3.0545</v>
@@ -2185,6 +2365,9 @@
       <c r="H60" s="3" t="n">
         <v>3.0545</v>
       </c>
+      <c r="I60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2199,13 +2382,13 @@
         <v>3.38</v>
       </c>
       <c r="D61" s="3" t="n">
+        <v>3.2847</v>
+      </c>
+      <c r="E61" s="3" t="n">
         <v>4.275</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="F61" s="3" t="n">
         <v>4.3798</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>3.95</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>3.95</v>
@@ -2213,6 +2396,9 @@
       <c r="H61" s="3" t="n">
         <v>3.95</v>
       </c>
+      <c r="I61" s="3" t="n">
+        <v>3.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2227,13 +2413,13 @@
         <v>3.4</v>
       </c>
       <c r="D62" s="3" t="n">
+        <v>3.3216</v>
+      </c>
+      <c r="E62" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="F62" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>4.685</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>4.685</v>
@@ -2241,6 +2427,9 @@
       <c r="H62" s="3" t="n">
         <v>4.685</v>
       </c>
+      <c r="I62" s="3" t="n">
+        <v>4.685</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2255,13 +2444,13 @@
         <v>2.06</v>
       </c>
       <c r="D63" s="3" t="n">
+        <v>1.877</v>
+      </c>
+      <c r="E63" s="3" t="n">
         <v>2.485</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="F63" s="3" t="n">
         <v>2.4509</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>2.571</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>2.571</v>
@@ -2269,6 +2458,9 @@
       <c r="H63" s="3" t="n">
         <v>2.571</v>
       </c>
+      <c r="I63" s="3" t="n">
+        <v>2.571</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2283,13 +2475,13 @@
         <v>3.31</v>
       </c>
       <c r="D64" s="3" t="n">
+        <v>3.3216</v>
+      </c>
+      <c r="E64" s="3" t="n">
         <v>3.555</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="F64" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>3.975</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>3.975</v>
@@ -2297,6 +2489,9 @@
       <c r="H64" s="3" t="n">
         <v>3.975</v>
       </c>
+      <c r="I64" s="3" t="n">
+        <v>3.975</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2311,13 +2506,13 @@
         <v>2.66</v>
       </c>
       <c r="D65" s="3" t="n">
+        <v>3.3707</v>
+      </c>
+      <c r="E65" s="3" t="n">
         <v>3.78</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="F65" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>4.346</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>4.346</v>
@@ -2325,6 +2520,9 @@
       <c r="H65" s="3" t="n">
         <v>4.346</v>
       </c>
+      <c r="I65" s="3" t="n">
+        <v>4.346</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2339,13 +2537,13 @@
         <v>3.425</v>
       </c>
       <c r="D66" s="3" t="n">
+        <v>3.3707</v>
+      </c>
+      <c r="E66" s="3" t="n">
         <v>4.36</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="F66" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>4.577</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>4.577</v>
@@ -2353,6 +2551,9 @@
       <c r="H66" s="3" t="n">
         <v>4.577</v>
       </c>
+      <c r="I66" s="3" t="n">
+        <v>4.577</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2367,13 +2568,13 @@
         <v>2.075</v>
       </c>
       <c r="D67" s="3" t="n">
+        <v>1.8739</v>
+      </c>
+      <c r="E67" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="F67" s="3" t="n">
         <v>2.4426</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>2.4315</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>2.4315</v>
@@ -2381,6 +2582,9 @@
       <c r="H67" s="3" t="n">
         <v>2.4315</v>
       </c>
+      <c r="I67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2395,13 +2599,13 @@
         <v>2.1</v>
       </c>
       <c r="D68" s="3" t="n">
+        <v>1.9653</v>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="F68" s="3" t="n">
         <v>2.5</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>2.484</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>2.484</v>
@@ -2409,6 +2613,9 @@
       <c r="H68" s="3" t="n">
         <v>2.484</v>
       </c>
+      <c r="I68" s="3" t="n">
+        <v>2.484</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2423,13 +2630,13 @@
         <v>2.745</v>
       </c>
       <c r="D69" s="3" t="n">
+        <v>2.6878</v>
+      </c>
+      <c r="E69" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="F69" s="3" t="n">
         <v>2.8253</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>2.892</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>2.892</v>
@@ -2437,6 +2644,9 @@
       <c r="H69" s="3" t="n">
         <v>2.892</v>
       </c>
+      <c r="I69" s="3" t="n">
+        <v>2.892</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2451,13 +2661,13 @@
         <v>-1.78</v>
       </c>
       <c r="D70" s="3" t="n">
+        <v>-2.4994</v>
+      </c>
+      <c r="E70" s="3" t="n">
         <v>1.495</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="F70" s="3" t="n">
         <v>1.8123</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>1.38</v>
@@ -2465,9 +2675,12 @@
       <c r="H70" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="I70" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H70"/>
+  <autoFilter ref="A1:I70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -553,7 +553,7 @@
         <v>3.035</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.8483</v>
+        <v>2.86</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2.91</v>
@@ -584,7 +584,7 @@
         <v>2.46</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.2683</v>
+        <v>2.27</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>2.61</v>
@@ -615,7 +615,7 @@
         <v>2.175</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.25</v>
+        <v>2.295</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>2.61</v>
@@ -646,7 +646,7 @@
         <v>2.8</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.7135</v>
+        <v>2.715</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>2.78</v>
@@ -677,7 +677,7 @@
         <v>2.965</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.8395</v>
+        <v>2.84</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>2.8</v>
@@ -708,7 +708,7 @@
         <v>1.5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.3856</v>
+        <v>1.385</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.165</v>
@@ -739,7 +739,7 @@
         <v>1.5</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.4121</v>
+        <v>1.41</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>2.245</v>
@@ -770,7 +770,7 @@
         <v>2.635</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2.6346</v>
+        <v>2.64</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>2.76</v>
@@ -801,7 +801,7 @@
         <v>2.575</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.6033</v>
+        <v>2.605</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>2.75</v>
@@ -832,7 +832,7 @@
         <v>-1.8</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-2.5212</v>
+        <v>-2.455</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>1.5</v>
@@ -863,7 +863,7 @@
         <v>2.06</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1.8552</v>
+        <v>1.855</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>2.425</v>
@@ -894,7 +894,7 @@
         <v>2.73</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2.64</v>
+        <v>2.635</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>2.77</v>
@@ -925,7 +925,7 @@
         <v>2.535</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2.4</v>
+        <v>2.585</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>2.735</v>
@@ -956,7 +956,7 @@
         <v>3.555</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.4716</v>
+        <v>3.5</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>4.48</v>
@@ -987,7 +987,7 @@
         <v>2.835</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.732</v>
+        <v>2.73</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>2.74</v>
@@ -1018,7 +1018,7 @@
         <v>3.34</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.0859</v>
+        <v>3.085</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>3.215</v>
@@ -1080,7 +1080,7 @@
         <v>2.455</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2.5163</v>
+        <v>2.515</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>2.76</v>
@@ -1111,7 +1111,7 @@
         <v>2.81</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.7234</v>
+        <v>2.73</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>2.745</v>
@@ -1142,7 +1142,7 @@
         <v>1.54</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.3913</v>
+        <v>1.425</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>2.375</v>
@@ -1173,7 +1173,7 @@
         <v>2.5</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.5977</v>
+        <v>2.6</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>2.75</v>
@@ -1204,7 +1204,7 @@
         <v>1.97</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.8045</v>
+        <v>1.805</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>2.4</v>
@@ -1235,7 +1235,7 @@
         <v>2.63</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2.5842</v>
+        <v>2.59</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>2.665</v>
@@ -1266,7 +1266,7 @@
         <v>2.78</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>2.6527</v>
+        <v>2.655</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>2.715</v>
@@ -1297,7 +1297,7 @@
         <v>2.72</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2.6593</v>
+        <v>2.66</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>2.74</v>
@@ -1328,7 +1328,7 @@
         <v>2.5</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.4697</v>
+        <v>2.47</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>2.74</v>
@@ -1359,7 +1359,7 @@
         <v>2.565</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2.5291</v>
+        <v>2.53</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>2.73</v>
@@ -1390,7 +1390,7 @@
         <v>1.49</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>2.245</v>
@@ -1421,7 +1421,7 @@
         <v>1.45</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1.244</v>
+        <v>1.345</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>1.245</v>
@@ -1452,7 +1452,7 @@
         <v>2.655</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.3698</v>
+        <v>2.37</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>2.65</v>
@@ -1483,7 +1483,7 @@
         <v>1.81</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1.6327</v>
+        <v>1.635</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>2.075</v>
@@ -1514,7 +1514,7 @@
         <v>1.495</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1.3703</v>
+        <v>1.37</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>1.41</v>
@@ -1545,7 +1545,7 @@
         <v>2.5</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>2.3405</v>
+        <v>2.34</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.64</v>
@@ -1576,7 +1576,7 @@
         <v>-1.8</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-2.4215</v>
+        <v>-2.455</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>1.51</v>
@@ -1607,7 +1607,7 @@
         <v>3.03</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.8835</v>
+        <v>2.885</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.93</v>
@@ -1638,7 +1638,7 @@
         <v>2.605</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>2.6377</v>
+        <v>2.64</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>2.725</v>
@@ -1669,7 +1669,7 @@
         <v>1.4</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1.2395</v>
+        <v>1.24</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>2.255</v>
@@ -1700,7 +1700,7 @@
         <v>1.415</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1.3731</v>
+        <v>1.375</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>2.6</v>
@@ -1731,7 +1731,7 @@
         <v>2.505</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>2.4226</v>
+        <v>2.425</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>3.29</v>
@@ -1762,7 +1762,7 @@
         <v>3.41</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>3.3317</v>
+        <v>3.33</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>4.315</v>
@@ -1793,7 +1793,7 @@
         <v>2.545</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>2.3954</v>
+        <v>2.395</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>2.615</v>
@@ -1824,7 +1824,7 @@
         <v>2.17</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>1.9892</v>
+        <v>1.99</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>2.56</v>
@@ -1855,7 +1855,7 @@
         <v>2.99</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>2.8703</v>
+        <v>2.87</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>2.915</v>
@@ -1886,7 +1886,7 @@
         <v>2.045</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.8598</v>
+        <v>1.86</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>2.42</v>
@@ -1917,7 +1917,7 @@
         <v>2.09</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1.9239</v>
+        <v>1.925</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>2.5</v>
@@ -1948,7 +1948,7 @@
         <v>2.835</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>2.736</v>
+        <v>2.735</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>2.72</v>
@@ -1979,7 +1979,7 @@
         <v>3.03</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.8699</v>
+        <v>2.87</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.905</v>
@@ -2010,7 +2010,7 @@
         <v>3.39</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>3.3178</v>
+        <v>3.32</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>4.295</v>
@@ -2041,7 +2041,7 @@
         <v>2.845</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2.7533</v>
+        <v>2.755</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>2.795</v>
@@ -2072,7 +2072,7 @@
         <v>2.78</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2.6528</v>
+        <v>2.655</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>2.715</v>
@@ -2103,7 +2103,7 @@
         <v>2.785</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2.699</v>
+        <v>2.61</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>2.76</v>
@@ -2134,7 +2134,7 @@
         <v>2.07</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1.9043</v>
+        <v>1.905</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2.54</v>
@@ -2165,7 +2165,7 @@
         <v>1.875</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1.7917</v>
+        <v>1.79</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>2.405</v>
@@ -2196,7 +2196,7 @@
         <v>2.365</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>2.65</v>
@@ -2227,7 +2227,7 @@
         <v>2.185</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>2.6</v>
@@ -2258,7 +2258,7 @@
         <v>2.8</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>2.7214</v>
+        <v>2.72</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>2.825</v>
@@ -2289,7 +2289,7 @@
         <v>2.14</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1.9239</v>
+        <v>1.95</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>2.525</v>
@@ -2320,7 +2320,7 @@
         <v>2.755</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2.4822</v>
+        <v>2.48</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>2.71</v>
@@ -2351,7 +2351,7 @@
         <v>2.93</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>2.8109</v>
+        <v>2.815</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>2.835</v>
@@ -2382,7 +2382,7 @@
         <v>3.38</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>3.2847</v>
+        <v>3.285</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>4.275</v>
@@ -2413,7 +2413,7 @@
         <v>3.4</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>3.3216</v>
+        <v>3.32</v>
       </c>
       <c r="E62" s="3" t="n">
         <v>4.33</v>
@@ -2444,7 +2444,7 @@
         <v>2.06</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.877</v>
+        <v>1.875</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>2.485</v>
@@ -2475,7 +2475,7 @@
         <v>3.31</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>3.3216</v>
+        <v>3.115</v>
       </c>
       <c r="E64" s="3" t="n">
         <v>3.555</v>
@@ -2506,7 +2506,7 @@
         <v>2.66</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>3.3707</v>
+        <v>2.88</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>3.78</v>
@@ -2537,7 +2537,7 @@
         <v>3.425</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>3.3707</v>
+        <v>3.37</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>4.36</v>
@@ -2568,7 +2568,7 @@
         <v>2.075</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1.8739</v>
+        <v>1.905</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>2.49</v>
@@ -2599,7 +2599,7 @@
         <v>2.1</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1.9653</v>
+        <v>1.965</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>2.525</v>
@@ -2630,7 +2630,7 @@
         <v>2.745</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>2.6878</v>
+        <v>2.69</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>2.77</v>
@@ -2661,7 +2661,7 @@
         <v>-1.78</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>-2.4994</v>
+        <v>-2.375</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>1.495</v>

--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -9,7 +9,7 @@
     <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$J$70</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -491,6 +491,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -516,25 +517,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
@@ -556,13 +562,13 @@
         <v>2.86</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>2.91</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>2.8799</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>2.9</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>2.9</v>
@@ -570,6 +576,9 @@
       <c r="I2" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="J2" s="3" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -587,13 +596,13 @@
         <v>2.27</v>
       </c>
       <c r="E3" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>2.6174</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>2.758</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>2.758</v>
@@ -601,6 +610,9 @@
       <c r="I3" s="3" t="n">
         <v>2.758</v>
       </c>
+      <c r="J3" s="3" t="n">
+        <v>2.758</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -618,13 +630,13 @@
         <v>2.295</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="G4" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>2.803</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>2.803</v>
@@ -632,6 +644,9 @@
       <c r="I4" s="3" t="n">
         <v>2.803</v>
       </c>
+      <c r="J4" s="3" t="n">
+        <v>2.803</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -649,13 +664,13 @@
         <v>2.715</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>2.814</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2.826</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>2.826</v>
@@ -663,6 +678,9 @@
       <c r="I5" s="3" t="n">
         <v>2.826</v>
       </c>
+      <c r="J5" s="3" t="n">
+        <v>2.826</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -680,13 +698,13 @@
         <v>2.84</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>2.8136</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>2.795</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>2.795</v>
@@ -694,6 +712,9 @@
       <c r="I6" s="3" t="n">
         <v>2.795</v>
       </c>
+      <c r="J6" s="3" t="n">
+        <v>2.795</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -711,13 +732,13 @@
         <v>1.385</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>2.165</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>1.935</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.815</v>
@@ -725,6 +746,9 @@
       <c r="I7" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="J7" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -742,13 +766,13 @@
         <v>1.41</v>
       </c>
       <c r="E8" s="3" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="G8" s="3" t="n">
         <v>1.958</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>1.815</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1.815</v>
@@ -756,6 +780,9 @@
       <c r="I8" s="3" t="n">
         <v>1.815</v>
       </c>
+      <c r="J8" s="3" t="n">
+        <v>1.815</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -773,13 +800,13 @@
         <v>2.64</v>
       </c>
       <c r="E9" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="F9" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="G9" s="3" t="n">
         <v>2.7246</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>2.83</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>2.83</v>
@@ -787,6 +814,9 @@
       <c r="I9" s="3" t="n">
         <v>2.83</v>
       </c>
+      <c r="J9" s="3" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -804,13 +834,13 @@
         <v>2.605</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>2.8088</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>2.78</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>2.78</v>
@@ -818,6 +848,9 @@
       <c r="I10" s="3" t="n">
         <v>2.78</v>
       </c>
+      <c r="J10" s="3" t="n">
+        <v>2.78</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -835,13 +868,13 @@
         <v>-2.455</v>
       </c>
       <c r="E11" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="F11" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="G11" s="3" t="n">
         <v>1.7466</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>1.204</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>1.204</v>
@@ -849,6 +882,9 @@
       <c r="I11" s="3" t="n">
         <v>1.204</v>
       </c>
+      <c r="J11" s="3" t="n">
+        <v>1.204</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -866,13 +902,13 @@
         <v>1.855</v>
       </c>
       <c r="E12" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>2.425</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="G12" s="3" t="n">
         <v>2.4222</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>2.485</v>
@@ -880,6 +916,9 @@
       <c r="I12" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="J12" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -897,13 +936,13 @@
         <v>2.635</v>
       </c>
       <c r="E13" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="F13" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>2.8214</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>2.832</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>2.832</v>
@@ -911,6 +950,9 @@
       <c r="I13" s="3" t="n">
         <v>2.832</v>
       </c>
+      <c r="J13" s="3" t="n">
+        <v>2.832</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -928,13 +970,13 @@
         <v>2.585</v>
       </c>
       <c r="E14" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>2.735</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="G14" s="3" t="n">
         <v>2.805</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>2.8</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>2.8</v>
@@ -942,6 +984,9 @@
       <c r="I14" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="J14" s="3" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -959,13 +1004,13 @@
         <v>3.5</v>
       </c>
       <c r="E15" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>4.48</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="G15" s="3" t="n">
         <v>4.5909</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>4.545</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>4.545</v>
@@ -973,6 +1018,9 @@
       <c r="I15" s="3" t="n">
         <v>4.545</v>
       </c>
+      <c r="J15" s="3" t="n">
+        <v>4.545</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -990,13 +1038,13 @@
         <v>2.73</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="G16" s="3" t="n">
         <v>2.7991</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2.55</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>2.55</v>
@@ -1004,6 +1052,9 @@
       <c r="I16" s="3" t="n">
         <v>2.55</v>
       </c>
+      <c r="J16" s="3" t="n">
+        <v>2.55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1021,13 +1072,13 @@
         <v>3.085</v>
       </c>
       <c r="E17" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="F17" s="3" t="n">
         <v>3.215</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="G17" s="3" t="n">
         <v>3.2871</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>3.285</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>3.285</v>
@@ -1035,6 +1086,9 @@
       <c r="I17" s="3" t="n">
         <v>3.285</v>
       </c>
+      <c r="J17" s="3" t="n">
+        <v>3.285</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1052,13 +1106,13 @@
         <v>2.53</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>2.69</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="G18" s="3" t="n">
         <v>2.799</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>2.59</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>2.59</v>
@@ -1066,6 +1120,9 @@
       <c r="I18" s="3" t="n">
         <v>2.59</v>
       </c>
+      <c r="J18" s="3" t="n">
+        <v>2.59</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1083,13 +1140,13 @@
         <v>2.515</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>2.76</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>2.8072</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>2.5835</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>2.5835</v>
@@ -1097,6 +1154,9 @@
       <c r="I19" s="3" t="n">
         <v>2.5835</v>
       </c>
+      <c r="J19" s="3" t="n">
+        <v>2.5835</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1114,13 +1174,13 @@
         <v>2.73</v>
       </c>
       <c r="E20" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>2.745</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>2.788</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>2.5755</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>2.5755</v>
@@ -1128,6 +1188,9 @@
       <c r="I20" s="3" t="n">
         <v>2.5755</v>
       </c>
+      <c r="J20" s="3" t="n">
+        <v>2.5755</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1145,13 +1208,13 @@
         <v>1.425</v>
       </c>
       <c r="E21" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>2.375</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2.156</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>2.156</v>
@@ -1159,6 +1222,9 @@
       <c r="I21" s="3" t="n">
         <v>2.156</v>
       </c>
+      <c r="J21" s="3" t="n">
+        <v>2.156</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1176,13 +1242,13 @@
         <v>2.6</v>
       </c>
       <c r="E22" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F22" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="G22" s="3" t="n">
         <v>2.8098</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>2.866</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>2.866</v>
@@ -1190,6 +1256,9 @@
       <c r="I22" s="3" t="n">
         <v>2.866</v>
       </c>
+      <c r="J22" s="3" t="n">
+        <v>2.866</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1207,13 +1276,13 @@
         <v>1.805</v>
       </c>
       <c r="E23" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F23" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="G23" s="3" t="n">
         <v>2.35</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>2.525</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>2.525</v>
@@ -1221,6 +1290,9 @@
       <c r="I23" s="3" t="n">
         <v>2.525</v>
       </c>
+      <c r="J23" s="3" t="n">
+        <v>2.525</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1238,13 +1310,13 @@
         <v>2.59</v>
       </c>
       <c r="E24" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="F24" s="3" t="n">
         <v>2.665</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="G24" s="3" t="n">
         <v>2.6798</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>2.781</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>2.781</v>
@@ -1252,6 +1324,9 @@
       <c r="I24" s="3" t="n">
         <v>2.781</v>
       </c>
+      <c r="J24" s="3" t="n">
+        <v>2.781</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1269,13 +1344,13 @@
         <v>2.655</v>
       </c>
       <c r="E25" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="G25" s="3" t="n">
         <v>2.7689</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>2.81</v>
@@ -1283,6 +1358,9 @@
       <c r="I25" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="J25" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1300,13 +1378,13 @@
         <v>2.66</v>
       </c>
       <c r="E26" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="G26" s="3" t="n">
         <v>2.7496</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>2.81</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>2.81</v>
@@ -1314,6 +1392,9 @@
       <c r="I26" s="3" t="n">
         <v>2.81</v>
       </c>
+      <c r="J26" s="3" t="n">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1331,13 +1412,13 @@
         <v>2.47</v>
       </c>
       <c r="E27" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F27" s="3" t="n">
         <v>2.74</v>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="G27" s="3" t="n">
         <v>2.662</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>2.79</v>
@@ -1345,6 +1426,9 @@
       <c r="I27" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="J27" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1362,13 +1446,13 @@
         <v>2.53</v>
       </c>
       <c r="E28" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>2.73</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="G28" s="3" t="n">
         <v>2.6808</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>2.84</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>2.84</v>
@@ -1376,6 +1460,9 @@
       <c r="I28" s="3" t="n">
         <v>2.84</v>
       </c>
+      <c r="J28" s="3" t="n">
+        <v>2.84</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1393,13 +1480,13 @@
         <v>1.38</v>
       </c>
       <c r="E29" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>2.245</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="G29" s="3" t="n">
         <v>2.05</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>1.99</v>
@@ -1407,6 +1494,9 @@
       <c r="I29" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="J29" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1424,10 +1514,10 @@
         <v>1.345</v>
       </c>
       <c r="E30" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F30" s="3" t="n">
         <v>1.245</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>1.572</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>1.572</v>
@@ -1438,6 +1528,9 @@
       <c r="I30" s="3" t="n">
         <v>1.572</v>
       </c>
+      <c r="J30" s="3" t="n">
+        <v>1.572</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1455,13 +1548,13 @@
         <v>2.37</v>
       </c>
       <c r="E31" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="F31" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="G31" s="3" t="n">
         <v>2.6526</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>2.6865</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>2.6865</v>
@@ -1469,6 +1562,9 @@
       <c r="I31" s="3" t="n">
         <v>2.6865</v>
       </c>
+      <c r="J31" s="3" t="n">
+        <v>2.6865</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1486,13 +1582,13 @@
         <v>1.635</v>
       </c>
       <c r="E32" s="3" t="n">
+        <v>1.655</v>
+      </c>
+      <c r="F32" s="3" t="n">
         <v>2.075</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="G32" s="3" t="n">
         <v>1.9591</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.99</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>1.99</v>
@@ -1500,6 +1596,9 @@
       <c r="I32" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="J32" s="3" t="n">
+        <v>1.99</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1517,13 +1616,13 @@
         <v>1.37</v>
       </c>
       <c r="E33" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>1.41</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>1.3192</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>1.34</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>1.34</v>
@@ -1531,6 +1630,9 @@
       <c r="I33" s="3" t="n">
         <v>1.34</v>
       </c>
+      <c r="J33" s="3" t="n">
+        <v>1.34</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1548,13 +1650,13 @@
         <v>2.34</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>2.64</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="G34" s="3" t="n">
         <v>2.6338</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2.71</v>
@@ -1562,6 +1664,9 @@
       <c r="I34" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="J34" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1579,13 +1684,13 @@
         <v>-2.455</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>-1.695</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>1.51</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="G35" s="3" t="n">
         <v>1.7958</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>1.38</v>
@@ -1593,6 +1698,9 @@
       <c r="I35" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="J35" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1610,13 +1718,13 @@
         <v>2.885</v>
       </c>
       <c r="E36" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>2.93</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="G36" s="3" t="n">
         <v>2.9677</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.992</v>
@@ -1624,6 +1732,9 @@
       <c r="I36" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="J36" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1641,13 +1752,13 @@
         <v>2.64</v>
       </c>
       <c r="E37" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>2.725</v>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="G37" s="3" t="n">
         <v>2.7289</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>2.785</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>2.785</v>
@@ -1655,6 +1766,9 @@
       <c r="I37" s="3" t="n">
         <v>2.785</v>
       </c>
+      <c r="J37" s="3" t="n">
+        <v>2.785</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1672,13 +1786,13 @@
         <v>1.24</v>
       </c>
       <c r="E38" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F38" s="3" t="n">
         <v>2.255</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="G38" s="3" t="n">
         <v>2.007</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>2.135</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>2.135</v>
@@ -1686,6 +1800,9 @@
       <c r="I38" s="3" t="n">
         <v>2.135</v>
       </c>
+      <c r="J38" s="3" t="n">
+        <v>2.135</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1703,13 +1820,13 @@
         <v>1.375</v>
       </c>
       <c r="E39" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="G39" s="3" t="n">
         <v>2.5482</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>2.485</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>2.485</v>
@@ -1717,6 +1834,9 @@
       <c r="I39" s="3" t="n">
         <v>2.485</v>
       </c>
+      <c r="J39" s="3" t="n">
+        <v>2.485</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1734,13 +1854,13 @@
         <v>2.425</v>
       </c>
       <c r="E40" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F40" s="3" t="n">
         <v>3.29</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="G40" s="3" t="n">
         <v>3.2201</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>3.375</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>3.375</v>
@@ -1748,6 +1868,9 @@
       <c r="I40" s="3" t="n">
         <v>3.375</v>
       </c>
+      <c r="J40" s="3" t="n">
+        <v>3.375</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1765,13 +1888,13 @@
         <v>3.33</v>
       </c>
       <c r="E41" s="3" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>4.315</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="G41" s="3" t="n">
         <v>4.4174</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>4.363</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>4.363</v>
@@ -1779,6 +1902,9 @@
       <c r="I41" s="3" t="n">
         <v>4.363</v>
       </c>
+      <c r="J41" s="3" t="n">
+        <v>4.363</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1796,13 +1922,13 @@
         <v>2.395</v>
       </c>
       <c r="E42" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="F42" s="3" t="n">
         <v>2.615</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" s="3" t="n">
         <v>2.6647</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>2.71</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>2.71</v>
@@ -1810,6 +1936,9 @@
       <c r="I42" s="3" t="n">
         <v>2.71</v>
       </c>
+      <c r="J42" s="3" t="n">
+        <v>2.71</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1827,13 +1956,13 @@
         <v>1.99</v>
       </c>
       <c r="E43" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="F43" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="G43" s="3" t="n">
         <v>2.5612</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>2.6805</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>2.6805</v>
@@ -1841,6 +1970,9 @@
       <c r="I43" s="3" t="n">
         <v>2.6805</v>
       </c>
+      <c r="J43" s="3" t="n">
+        <v>2.6805</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1858,13 +1990,13 @@
         <v>2.87</v>
       </c>
       <c r="E44" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>2.915</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="G44" s="3" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>3.042</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>3.042</v>
@@ -1872,6 +2004,9 @@
       <c r="I44" s="3" t="n">
         <v>3.042</v>
       </c>
+      <c r="J44" s="3" t="n">
+        <v>3.042</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1889,13 +2024,13 @@
         <v>1.86</v>
       </c>
       <c r="E45" s="3" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="F45" s="3" t="n">
         <v>2.42</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="G45" s="3" t="n">
         <v>2.4175</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>2.475</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>2.475</v>
@@ -1903,6 +2038,9 @@
       <c r="I45" s="3" t="n">
         <v>2.475</v>
       </c>
+      <c r="J45" s="3" t="n">
+        <v>2.475</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1920,13 +2058,13 @@
         <v>1.925</v>
       </c>
       <c r="E46" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="G46" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2.48</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>2.48</v>
@@ -1934,6 +2072,9 @@
       <c r="I46" s="3" t="n">
         <v>2.48</v>
       </c>
+      <c r="J46" s="3" t="n">
+        <v>2.48</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1951,13 +2092,13 @@
         <v>2.735</v>
       </c>
       <c r="E47" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F47" s="3" t="n">
         <v>2.72</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="G47" s="3" t="n">
         <v>2.7743</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>2.786</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>2.786</v>
@@ -1965,6 +2106,9 @@
       <c r="I47" s="3" t="n">
         <v>2.786</v>
       </c>
+      <c r="J47" s="3" t="n">
+        <v>2.786</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1982,13 +2126,13 @@
         <v>2.87</v>
       </c>
       <c r="E48" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="F48" s="3" t="n">
         <v>2.905</v>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="G48" s="3" t="n">
         <v>2.9772</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>2.992</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>2.992</v>
@@ -1996,6 +2140,9 @@
       <c r="I48" s="3" t="n">
         <v>2.992</v>
       </c>
+      <c r="J48" s="3" t="n">
+        <v>2.992</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2013,13 +2160,13 @@
         <v>3.32</v>
       </c>
       <c r="E49" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="F49" s="3" t="n">
         <v>4.295</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="G49" s="3" t="n">
         <v>4.3206</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>4.245</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>4.245</v>
@@ -2027,6 +2174,9 @@
       <c r="I49" s="3" t="n">
         <v>4.245</v>
       </c>
+      <c r="J49" s="3" t="n">
+        <v>4.245</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2044,13 +2194,13 @@
         <v>2.755</v>
       </c>
       <c r="E50" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="F50" s="3" t="n">
         <v>2.795</v>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="G50" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>2.932</v>
@@ -2058,6 +2208,9 @@
       <c r="I50" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="J50" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2075,13 +2228,13 @@
         <v>2.655</v>
       </c>
       <c r="E51" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F51" s="3" t="n">
         <v>2.715</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="G51" s="3" t="n">
         <v>2.768</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>2.79</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>2.79</v>
@@ -2089,6 +2242,9 @@
       <c r="I51" s="3" t="n">
         <v>2.79</v>
       </c>
+      <c r="J51" s="3" t="n">
+        <v>2.79</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2106,10 +2262,10 @@
         <v>2.61</v>
       </c>
       <c r="E52" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="F52" s="3" t="n">
         <v>2.76</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>2.932</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>2.932</v>
@@ -2120,6 +2276,9 @@
       <c r="I52" s="3" t="n">
         <v>2.932</v>
       </c>
+      <c r="J52" s="3" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2137,13 +2296,13 @@
         <v>1.905</v>
       </c>
       <c r="E53" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F53" s="3" t="n">
         <v>2.54</v>
       </c>
-      <c r="F53" s="3" t="n">
+      <c r="G53" s="3" t="n">
         <v>2.5115</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>2.685</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>2.685</v>
@@ -2151,6 +2310,9 @@
       <c r="I53" s="3" t="n">
         <v>2.685</v>
       </c>
+      <c r="J53" s="3" t="n">
+        <v>2.685</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2168,13 +2330,13 @@
         <v>1.79</v>
       </c>
       <c r="E54" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="F54" s="3" t="n">
         <v>2.405</v>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="G54" s="3" t="n">
         <v>2.3724</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>2.4125</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>2.4125</v>
@@ -2182,6 +2344,9 @@
       <c r="I54" s="3" t="n">
         <v>2.4125</v>
       </c>
+      <c r="J54" s="3" t="n">
+        <v>2.4125</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2199,13 +2364,13 @@
         <v>2.25</v>
       </c>
       <c r="E55" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="F55" s="3" t="n">
         <v>2.65</v>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="G55" s="3" t="n">
         <v>3.15</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>2.6755</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>2.6755</v>
@@ -2213,6 +2378,9 @@
       <c r="I55" s="3" t="n">
         <v>2.6755</v>
       </c>
+      <c r="J55" s="3" t="n">
+        <v>2.6755</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2230,13 +2398,13 @@
         <v>2.16</v>
       </c>
       <c r="E56" s="3" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="G56" s="3" t="n">
         <v>2.95</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>2.581</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>2.581</v>
@@ -2244,6 +2412,9 @@
       <c r="I56" s="3" t="n">
         <v>2.581</v>
       </c>
+      <c r="J56" s="3" t="n">
+        <v>2.581</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2261,13 +2432,13 @@
         <v>2.72</v>
       </c>
       <c r="E57" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="F57" s="3" t="n">
         <v>2.825</v>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="G57" s="3" t="n">
         <v>2.8203</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>2.934</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>2.934</v>
@@ -2275,6 +2446,9 @@
       <c r="I57" s="3" t="n">
         <v>2.934</v>
       </c>
+      <c r="J57" s="3" t="n">
+        <v>2.934</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2292,13 +2466,13 @@
         <v>1.95</v>
       </c>
       <c r="E58" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F58" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="G58" s="3" t="n">
         <v>2.4926</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>2.36</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>2.36</v>
@@ -2306,6 +2480,9 @@
       <c r="I58" s="3" t="n">
         <v>2.36</v>
       </c>
+      <c r="J58" s="3" t="n">
+        <v>2.36</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2323,13 +2500,13 @@
         <v>2.48</v>
       </c>
       <c r="E59" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="F59" s="3" t="n">
         <v>2.71</v>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="G59" s="3" t="n">
         <v>2.83</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>2.766</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>2.766</v>
@@ -2337,6 +2514,9 @@
       <c r="I59" s="3" t="n">
         <v>2.766</v>
       </c>
+      <c r="J59" s="3" t="n">
+        <v>2.766</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2354,13 +2534,13 @@
         <v>2.815</v>
       </c>
       <c r="E60" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="F60" s="3" t="n">
         <v>2.835</v>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="G60" s="3" t="n">
         <v>2.8382</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>3.0545</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>3.0545</v>
@@ -2368,6 +2548,9 @@
       <c r="I60" s="3" t="n">
         <v>3.0545</v>
       </c>
+      <c r="J60" s="3" t="n">
+        <v>3.0545</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2385,13 +2568,13 @@
         <v>3.285</v>
       </c>
       <c r="E61" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F61" s="3" t="n">
         <v>4.275</v>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="G61" s="3" t="n">
         <v>4.3798</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>3.95</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>3.95</v>
@@ -2399,6 +2582,9 @@
       <c r="I61" s="3" t="n">
         <v>3.95</v>
       </c>
+      <c r="J61" s="3" t="n">
+        <v>3.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2416,13 +2602,13 @@
         <v>3.32</v>
       </c>
       <c r="E62" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F62" s="3" t="n">
         <v>4.33</v>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="G62" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>4.685</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>4.685</v>
@@ -2430,6 +2616,9 @@
       <c r="I62" s="3" t="n">
         <v>4.685</v>
       </c>
+      <c r="J62" s="3" t="n">
+        <v>4.685</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2447,13 +2636,13 @@
         <v>1.875</v>
       </c>
       <c r="E63" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="F63" s="3" t="n">
         <v>2.485</v>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="G63" s="3" t="n">
         <v>2.4509</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>2.571</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>2.571</v>
@@ -2461,6 +2650,9 @@
       <c r="I63" s="3" t="n">
         <v>2.571</v>
       </c>
+      <c r="J63" s="3" t="n">
+        <v>2.571</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2478,13 +2670,13 @@
         <v>3.115</v>
       </c>
       <c r="E64" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F64" s="3" t="n">
         <v>3.555</v>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="G64" s="3" t="n">
         <v>4.4409</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>3.975</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>3.975</v>
@@ -2492,6 +2684,9 @@
       <c r="I64" s="3" t="n">
         <v>3.975</v>
       </c>
+      <c r="J64" s="3" t="n">
+        <v>3.975</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2509,13 +2704,13 @@
         <v>2.88</v>
       </c>
       <c r="E65" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>3.78</v>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="G65" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>4.346</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>4.346</v>
@@ -2523,6 +2718,9 @@
       <c r="I65" s="3" t="n">
         <v>4.346</v>
       </c>
+      <c r="J65" s="3" t="n">
+        <v>4.346</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2540,13 +2738,13 @@
         <v>3.37</v>
       </c>
       <c r="E66" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F66" s="3" t="n">
         <v>4.36</v>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="G66" s="3" t="n">
         <v>4.4485</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>4.577</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>4.577</v>
@@ -2554,6 +2752,9 @@
       <c r="I66" s="3" t="n">
         <v>4.577</v>
       </c>
+      <c r="J66" s="3" t="n">
+        <v>4.577</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2571,13 +2772,13 @@
         <v>1.905</v>
       </c>
       <c r="E67" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="F67" s="3" t="n">
         <v>2.49</v>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="G67" s="3" t="n">
         <v>2.4426</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>2.4315</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>2.4315</v>
@@ -2585,6 +2786,9 @@
       <c r="I67" s="3" t="n">
         <v>2.4315</v>
       </c>
+      <c r="J67" s="3" t="n">
+        <v>2.4315</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2602,13 +2806,13 @@
         <v>1.965</v>
       </c>
       <c r="E68" s="3" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="F68" s="3" t="n">
         <v>2.525</v>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="G68" s="3" t="n">
         <v>2.5</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>2.484</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>2.484</v>
@@ -2616,6 +2820,9 @@
       <c r="I68" s="3" t="n">
         <v>2.484</v>
       </c>
+      <c r="J68" s="3" t="n">
+        <v>2.484</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2633,13 +2840,13 @@
         <v>2.69</v>
       </c>
       <c r="E69" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="F69" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="G69" s="3" t="n">
         <v>2.8253</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>2.892</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>2.892</v>
@@ -2647,6 +2854,9 @@
       <c r="I69" s="3" t="n">
         <v>2.892</v>
       </c>
+      <c r="J69" s="3" t="n">
+        <v>2.892</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2664,13 +2874,13 @@
         <v>-2.375</v>
       </c>
       <c r="E70" s="3" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="F70" s="3" t="n">
         <v>1.495</v>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="G70" s="3" t="n">
         <v>1.8123</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>1.38</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>1.38</v>
@@ -2678,9 +2888,12 @@
       <c r="I70" s="3" t="n">
         <v>1.38</v>
       </c>
+      <c r="J70" s="3" t="n">
+        <v>1.38</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I70"/>
+  <autoFilter ref="A1:J70"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/master/master_ng_swing_gdd.xlsx
+++ b/master/master_ng_swing_gdd.xlsx
@@ -1,71 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfeinstein\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5077548E-221B-4B6D-B9FF-E0BEFF7CA29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{CF7D4A7D-AFDD-47A7-8305-EA9FCA254F9C}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="NG Swing GDD" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NG Swing GDD'!$A$1:$BR$3</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Date</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -73,26 +53,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -412,16 +474,868 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08032914-A696-480A-A89E-601ACF0B10D8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BR3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="16" customWidth="1" min="47" max="47"/>
+    <col width="16" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="49" max="49"/>
+    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="16" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="16" customWidth="1" min="53" max="53"/>
+    <col width="16" customWidth="1" min="54" max="54"/>
+    <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
+    <col width="16" customWidth="1" min="57" max="57"/>
+    <col width="16" customWidth="1" min="58" max="58"/>
+    <col width="16" customWidth="1" min="59" max="59"/>
+    <col width="16" customWidth="1" min="60" max="60"/>
+    <col width="16" customWidth="1" min="61" max="61"/>
+    <col width="16" customWidth="1" min="62" max="62"/>
+    <col width="16" customWidth="1" min="63" max="63"/>
+    <col width="16" customWidth="1" min="64" max="64"/>
+    <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
+    <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
+    <col width="16" customWidth="1" min="70" max="70"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ANR-SE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ANR-SW</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Algonquin</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CG-Mainline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CG-Onshore</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CIG</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cheyenne Hub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Consumers</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>EP West Texas</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Eastern Gas-South</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Enable Gas</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Enbridge-Dawn</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>FGT-Z3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>HSC</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Iroquois (into)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Iroquois-Z2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Katy</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Kern Delivered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Michcon</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Millennium East Pool</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>NGPL-Midcont Pool</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>NGPL-STX</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>NGPL-TxOk</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>NNG-Demarc</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>NNG-Ventura</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>NWP-Rockies</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>NWP-Sumas</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ONEOK</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>PG&amp;E-Citygate</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>PGT-Malin</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Panhandle</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Permian (EP)</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Pine Prairie</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>REX-Z3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>San Juan (EP)</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Socal-Border</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Socal-Citygate</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Sonat-Z0</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Southern Star</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>TCO</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>TETCO-ELA</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>TETCO-M2 (receipts)</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>TETCO-M3</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>TETCO-STX</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>TETCO-WLA</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-500L</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-800L</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-Z0</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-Z1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-Z4 200L</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-Z4 300L</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-Z6 200L North</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>TGP-Z6 200L South</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>TGT (Zone 1)</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-165</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-30</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-45</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-65</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-85</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-Leidy</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-Z3</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-Z5</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-Z5 South</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-Z6  (non-NY)</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Transco-Z6 (NY)</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Trunkline-Z1A</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Waha</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2.295</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>2.605</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>-2.455</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>2.585</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>3.085</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>-2.455</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL2" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM2" s="3" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="AN2" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AP2" s="3" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AR2" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AS2" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT2" s="3" t="n">
+        <v>1.925</v>
+      </c>
+      <c r="AU2" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AV2" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW2" s="3" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AX2" s="3" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="AY2" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="AZ2" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BA2" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="BB2" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BC2" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD2" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BE2" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BF2" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BG2" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BH2" s="3" t="n">
+        <v>2.815</v>
+      </c>
+      <c r="BI2" s="3" t="n">
+        <v>3.285</v>
+      </c>
+      <c r="BJ2" s="3" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BK2" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BL2" s="3" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="BM2" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BN2" s="3" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BO2" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="BP2" s="3" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="BQ2" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BR2" s="3" t="n">
+        <v>-2.375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>2.425</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>1.655</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>-1.695</v>
+      </c>
+      <c r="AJ3" s="3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL3" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM3" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN3" s="3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AO3" s="3" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="AP3" s="3" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="AQ3" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AR3" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="AS3" s="3" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>1.915</v>
+      </c>
+      <c r="AU3" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AV3" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AW3" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AX3" s="3" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="AY3" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AZ3" s="3" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="BA3" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB3" s="3" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="BC3" s="3" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="BD3" s="3" t="n">
+        <v>1.985</v>
+      </c>
+      <c r="BE3" s="3" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="BF3" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BG3" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH3" s="3" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="BI3" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ3" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK3" s="3" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="BL3" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BM3" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BN3" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BO3" s="3" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="BP3" s="3" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="BQ3" s="3" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="BR3" s="3" t="n">
+        <v>-1.75</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BR3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>